--- a/crime_data.xlsx
+++ b/crime_data.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13996419239</v>
+        <v>14811833563</v>
       </c>
       <c r="C2" t="n">
         <v>10181</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9838715103</v>
+        <v>14359866175</v>
       </c>
       <c r="C3" t="n">
         <v>10142</v>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18097722907</v>
+        <v>10345695687</v>
       </c>
       <c r="C4" t="n">
         <v>10276</v>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11667177512</v>
+        <v>14934502256</v>
       </c>
       <c r="C5" t="n">
         <v>8427</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18386241172</v>
+        <v>21714063705</v>
       </c>
       <c r="C6" t="n">
         <v>10401</v>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24758068702</v>
+        <v>14450932137</v>
       </c>
       <c r="C7" t="n">
         <v>11196</v>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25316427638</v>
+        <v>24613526943</v>
       </c>
       <c r="C8" t="n">
         <v>10403</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24354994795</v>
+        <v>21615494869</v>
       </c>
       <c r="C9" t="n">
         <v>9045</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21110637956</v>
+        <v>16069000634</v>
       </c>
       <c r="C10" t="n">
         <v>8786</v>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13688284923</v>
+        <v>17247482181</v>
       </c>
       <c r="C11" t="n">
         <v>6939</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35657240433</v>
+        <v>30517059143</v>
       </c>
       <c r="C12" t="n">
         <v>9981</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24043191129</v>
+        <v>27983132434</v>
       </c>
       <c r="C13" t="n">
         <v>10293</v>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19528834476</v>
+        <v>21379023145</v>
       </c>
       <c r="C14" t="n">
         <v>7322</v>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19025095867</v>
+        <v>15842528047</v>
       </c>
       <c r="C15" t="n">
         <v>14406</v>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15443647333</v>
+        <v>20310331826</v>
       </c>
       <c r="C16" t="n">
         <v>10332</v>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23293221081</v>
+        <v>35956011833</v>
       </c>
       <c r="C17" t="n">
         <v>15664</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15907442565</v>
+        <v>15609441447</v>
       </c>
       <c r="C18" t="n">
         <v>12342</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15759120158</v>
+        <v>18641035217</v>
       </c>
       <c r="C19" t="n">
         <v>8730</v>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21077997436</v>
+        <v>14785792420</v>
       </c>
       <c r="C20" t="n">
         <v>15764</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17598868606</v>
+        <v>26923234514</v>
       </c>
       <c r="C22" t="n">
         <v>16391</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14393636080</v>
+        <v>22488566111</v>
       </c>
       <c r="C23" t="n">
         <v>17536</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>35294135421</v>
+        <v>21251196973</v>
       </c>
       <c r="C24" t="n">
         <v>33190</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31856552551</v>
+        <v>32411658313</v>
       </c>
       <c r="C25" t="n">
         <v>19498</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17569662193</v>
+        <v>21602707031</v>
       </c>
       <c r="C26" t="n">
         <v>12097</v>

--- a/crime_data.xlsx
+++ b/crime_data.xlsx
@@ -425,36 +425,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>시도명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>지자체명</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>범죄예방예산(원)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>총범죄발생건수(건)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>인구수(명)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1만명당범죄율(건)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
@@ -463,600 +468,6641 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>서울 종로구</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>14811833563</v>
-      </c>
       <c r="C2" t="n">
+        <v>13621203978</v>
+      </c>
+      <c r="D2" t="n">
         <v>10181</v>
       </c>
-      <c r="D2" t="n">
-        <v>141000</v>
-      </c>
       <c r="E2" t="n">
-        <v>722.0599999999999</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>역사/도심 관광지 및 야간 공동화</t>
+        <v>216146</v>
+      </c>
+      <c r="F2" t="n">
+        <v>471.02</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>서울 중구</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>14359866175</v>
-      </c>
       <c r="C3" t="n">
+        <v>12387301304</v>
+      </c>
+      <c r="D3" t="n">
         <v>10142</v>
       </c>
-      <c r="D3" t="n">
-        <v>120000</v>
-      </c>
       <c r="E3" t="n">
-        <v>845.17</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>도심 업무 중심지 및 야간 공동화</t>
+        <v>209551</v>
+      </c>
+      <c r="F3" t="n">
+        <v>483.99</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>서울 용산구</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>10345695687</v>
-      </c>
       <c r="C4" t="n">
+        <v>16783720447</v>
+      </c>
+      <c r="D4" t="n">
         <v>10276</v>
       </c>
-      <c r="D4" t="n">
-        <v>217000</v>
-      </c>
       <c r="E4" t="n">
-        <v>473.55</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>교통 요충지 및 외국인 상권</t>
+        <v>258565</v>
+      </c>
+      <c r="F4" t="n">
+        <v>397.42</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>서울 성동구</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>14934502256</v>
-      </c>
       <c r="C5" t="n">
+        <v>17031654032</v>
+      </c>
+      <c r="D5" t="n">
         <v>8427</v>
       </c>
-      <c r="D5" t="n">
-        <v>279000</v>
-      </c>
       <c r="E5" t="n">
-        <v>302.04</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>성수동 카페거리 및 첨단산업</t>
+        <v>281704</v>
+      </c>
+      <c r="F5" t="n">
+        <v>299.14</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>서울 광진구</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>21714063705</v>
-      </c>
       <c r="C6" t="n">
+        <v>15657879940</v>
+      </c>
+      <c r="D6" t="n">
         <v>10401</v>
       </c>
-      <c r="D6" t="n">
-        <v>336000</v>
-      </c>
       <c r="E6" t="n">
-        <v>309.55</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>대학가 및 건대 상권</t>
+        <v>311295</v>
+      </c>
+      <c r="F6" t="n">
+        <v>334.12</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>서울 동대문구</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>14450932137</v>
-      </c>
       <c r="C7" t="n">
+        <v>14179513724</v>
+      </c>
+      <c r="D7" t="n">
         <v>11196</v>
       </c>
-      <c r="D7" t="n">
-        <v>342000</v>
-      </c>
       <c r="E7" t="n">
-        <v>327.37</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>패션상권 및 전통시장</t>
+        <v>354400</v>
+      </c>
+      <c r="F7" t="n">
+        <v>315.91</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>서울 중랑구</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>24613526943</v>
-      </c>
       <c r="C8" t="n">
+        <v>21581277277</v>
+      </c>
+      <c r="D8" t="n">
         <v>10403</v>
       </c>
-      <c r="D8" t="n">
-        <v>385000</v>
-      </c>
       <c r="E8" t="n">
-        <v>270.21</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>주거 밀집지역</t>
+        <v>443239</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234.7</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>서울 성북구</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>21615494869</v>
-      </c>
       <c r="C9" t="n">
+        <v>20714054417</v>
+      </c>
+      <c r="D9" t="n">
         <v>9045</v>
       </c>
-      <c r="D9" t="n">
-        <v>428000</v>
-      </c>
       <c r="E9" t="n">
-        <v>211.33</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>대학 밀집 및 단독주택지구</t>
+        <v>425428</v>
+      </c>
+      <c r="F9" t="n">
+        <v>212.61</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>서울 강북구</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>16069000634</v>
-      </c>
       <c r="C10" t="n">
+        <v>22346013944</v>
+      </c>
+      <c r="D10" t="n">
         <v>8786</v>
       </c>
-      <c r="D10" t="n">
-        <v>292000</v>
-      </c>
       <c r="E10" t="n">
-        <v>300.89</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>북한산 인접 베드타운</t>
+        <v>369604</v>
+      </c>
+      <c r="F10" t="n">
+        <v>237.71</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>서울 도봉구</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>17247482181</v>
-      </c>
       <c r="C11" t="n">
+        <v>20985269690</v>
+      </c>
+      <c r="D11" t="n">
         <v>6939</v>
       </c>
-      <c r="D11" t="n">
-        <v>310000</v>
-      </c>
       <c r="E11" t="n">
-        <v>223.84</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>베드타운 주거지역</t>
+        <v>340311</v>
+      </c>
+      <c r="F11" t="n">
+        <v>203.9</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>서울 노원구</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>30517059143</v>
-      </c>
       <c r="C12" t="n">
+        <v>31598466324</v>
+      </c>
+      <c r="D12" t="n">
         <v>9981</v>
       </c>
-      <c r="D12" t="n">
-        <v>501000</v>
-      </c>
       <c r="E12" t="n">
-        <v>199.22</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>대규모 아파트 단지 및 학원가</t>
+        <v>511186</v>
+      </c>
+      <c r="F12" t="n">
+        <v>195.25</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>서울 은평구</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>27983132434</v>
-      </c>
       <c r="C13" t="n">
+        <v>29794086221</v>
+      </c>
+      <c r="D13" t="n">
         <v>10293</v>
       </c>
-      <c r="D13" t="n">
-        <v>466000</v>
-      </c>
       <c r="E13" t="n">
-        <v>220.88</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>뉴타운 중심 주거지</t>
+        <v>459200</v>
+      </c>
+      <c r="F13" t="n">
+        <v>224.15</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>서울 서대문구</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>21379023145</v>
-      </c>
       <c r="C14" t="n">
+        <v>12476796500</v>
+      </c>
+      <c r="D14" t="n">
         <v>7322</v>
       </c>
-      <c r="D14" t="n">
-        <v>306000</v>
-      </c>
       <c r="E14" t="n">
-        <v>239.28</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>신촌 대학가 및 주거지</t>
+        <v>308651</v>
+      </c>
+      <c r="F14" t="n">
+        <v>237.23</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>서울 마포구</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>15842528047</v>
-      </c>
       <c r="C15" t="n">
+        <v>20586769020</v>
+      </c>
+      <c r="D15" t="n">
         <v>14406</v>
       </c>
-      <c r="D15" t="n">
-        <v>364000</v>
-      </c>
       <c r="E15" t="n">
-        <v>395.77</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>대학가 및 상권 밀집</t>
+        <v>322112</v>
+      </c>
+      <c r="F15" t="n">
+        <v>447.24</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>서울 양천구</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>20310331826</v>
-      </c>
       <c r="C16" t="n">
+        <v>23997553972</v>
+      </c>
+      <c r="D16" t="n">
         <v>10332</v>
       </c>
-      <c r="D16" t="n">
-        <v>438000</v>
-      </c>
       <c r="E16" t="n">
-        <v>235.89</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>목동 학원가 및 대형 단지</t>
+        <v>385976</v>
+      </c>
+      <c r="F16" t="n">
+        <v>267.69</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>서울 강서구</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>35956011833</v>
-      </c>
       <c r="C17" t="n">
+        <v>23379624439</v>
+      </c>
+      <c r="D17" t="n">
         <v>15664</v>
       </c>
-      <c r="D17" t="n">
-        <v>565000</v>
-      </c>
       <c r="E17" t="n">
-        <v>277.24</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>마곡R&amp;D 및 김포공항</t>
+        <v>513667</v>
+      </c>
+      <c r="F17" t="n">
+        <v>304.94</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>서울 구로구</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>15609441447</v>
-      </c>
       <c r="C18" t="n">
+        <v>15663163785</v>
+      </c>
+      <c r="D18" t="n">
         <v>12342</v>
       </c>
-      <c r="D18" t="n">
-        <v>393000</v>
-      </c>
       <c r="E18" t="n">
-        <v>314.05</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>디지털단지 및 외국인 밀집</t>
+        <v>390120</v>
+      </c>
+      <c r="F18" t="n">
+        <v>316.36</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>산업단지 및 다문화/공업 밀집</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>서울 금천구</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>18641035217</v>
-      </c>
       <c r="C19" t="n">
+        <v>18801909200</v>
+      </c>
+      <c r="D19" t="n">
         <v>8730</v>
       </c>
-      <c r="D19" t="n">
-        <v>228000</v>
-      </c>
       <c r="E19" t="n">
-        <v>382.89</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>가산디지털단지 및 공업지대</t>
+        <v>297259</v>
+      </c>
+      <c r="F19" t="n">
+        <v>293.68</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>산업단지 및 다문화/공업 밀집</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>서울 영등포구</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>14785792420</v>
-      </c>
       <c r="C20" t="n">
+        <v>22155623773</v>
+      </c>
+      <c r="D20" t="n">
         <v>15764</v>
       </c>
-      <c r="D20" t="n">
-        <v>374000</v>
-      </c>
       <c r="E20" t="n">
-        <v>421.5</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>금융 중심지 및 외국인 밀집지역</t>
+        <v>358424</v>
+      </c>
+      <c r="F20" t="n">
+        <v>439.81</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>서울 동작구</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>13924140325</v>
-      </c>
       <c r="C21" t="n">
+        <v>18231496804</v>
+      </c>
+      <c r="D21" t="n">
         <v>8849</v>
       </c>
-      <c r="D21" t="n">
-        <v>380000</v>
-      </c>
       <c r="E21" t="n">
-        <v>232.87</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>노량진 고시촌 및 주거지</t>
+        <v>348000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>254.28</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>서울 관악구</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>26923234514</v>
-      </c>
       <c r="C22" t="n">
+        <v>26081001740</v>
+      </c>
+      <c r="D22" t="n">
         <v>16391</v>
       </c>
-      <c r="D22" t="n">
-        <v>484000</v>
-      </c>
       <c r="E22" t="n">
-        <v>338.66</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1인 가구 및 청년층 비율 최고</t>
+        <v>413863</v>
+      </c>
+      <c r="F22" t="n">
+        <v>396.05</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>서울 서초구</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>22488566111</v>
-      </c>
       <c r="C23" t="n">
+        <v>21045003446</v>
+      </c>
+      <c r="D23" t="n">
         <v>17536</v>
       </c>
-      <c r="D23" t="n">
-        <v>404000</v>
-      </c>
       <c r="E23" t="n">
-        <v>434.06</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>법조타운 및 주거/상업 복합</t>
+        <v>338487</v>
+      </c>
+      <c r="F23" t="n">
+        <v>518.0700000000001</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>서울 강남구</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>21251196973</v>
-      </c>
       <c r="C24" t="n">
+        <v>33445354713</v>
+      </c>
+      <c r="D24" t="n">
         <v>33190</v>
       </c>
-      <c r="D24" t="n">
-        <v>533000</v>
-      </c>
       <c r="E24" t="n">
-        <v>622.7</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>상업/유흥 밀집 및 유동인구 최대</t>
+        <v>531231</v>
+      </c>
+      <c r="F24" t="n">
+        <v>624.78</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>서울 송파구</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>32411658313</v>
-      </c>
       <c r="C25" t="n">
+        <v>28482160190</v>
+      </c>
+      <c r="D25" t="n">
         <v>19498</v>
       </c>
-      <c r="D25" t="n">
-        <v>652000</v>
-      </c>
       <c r="E25" t="n">
-        <v>299.05</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>주거 밀집 및 대형 테마파크</t>
+        <v>471097</v>
+      </c>
+      <c r="F25" t="n">
+        <v>413.89</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>서울 강동구</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>21602707031</v>
-      </c>
       <c r="C26" t="n">
+        <v>18207993280</v>
+      </c>
+      <c r="D26" t="n">
         <v>12097</v>
       </c>
-      <c r="D26" t="n">
-        <v>460000</v>
-      </c>
       <c r="E26" t="n">
-        <v>262.98</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>신규 대단지 아파트 입주지역</t>
+        <v>423048</v>
+      </c>
+      <c r="F26" t="n">
+        <v>285.95</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>부산 중구</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3485726428</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3941</v>
+      </c>
+      <c r="E27" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>394.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>부산 서구</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6647881743</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3533</v>
+      </c>
+      <c r="E28" t="n">
+        <v>165429</v>
+      </c>
+      <c r="F28" t="n">
+        <v>213.57</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>부산 동구</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8960817876</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4439</v>
+      </c>
+      <c r="E29" t="n">
+        <v>150873</v>
+      </c>
+      <c r="F29" t="n">
+        <v>294.22</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>부산 영도구</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10584177393</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2759</v>
+      </c>
+      <c r="E30" t="n">
+        <v>171640</v>
+      </c>
+      <c r="F30" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>부산 진구</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>15309773164</v>
+      </c>
+      <c r="D31" t="n">
+        <v>17179</v>
+      </c>
+      <c r="E31" t="n">
+        <v>344382</v>
+      </c>
+      <c r="F31" t="n">
+        <v>498.84</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>부산 동래구</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>14707934090</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8519</v>
+      </c>
+      <c r="E32" t="n">
+        <v>230292</v>
+      </c>
+      <c r="F32" t="n">
+        <v>369.92</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>부산 남구</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>15355099045</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8356</v>
+      </c>
+      <c r="E33" t="n">
+        <v>266343</v>
+      </c>
+      <c r="F33" t="n">
+        <v>313.73</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>부산 북구</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17474727675</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6811</v>
+      </c>
+      <c r="E34" t="n">
+        <v>276777</v>
+      </c>
+      <c r="F34" t="n">
+        <v>246.08</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>부산 강서구</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7814568787</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5724</v>
+      </c>
+      <c r="E35" t="n">
+        <v>194863</v>
+      </c>
+      <c r="F35" t="n">
+        <v>293.74</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>부산 해운대구</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>22342380233</v>
+      </c>
+      <c r="D36" t="n">
+        <v>14389</v>
+      </c>
+      <c r="E36" t="n">
+        <v>346636</v>
+      </c>
+      <c r="F36" t="n">
+        <v>415.1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>부산 사하구</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>13286792333</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8232</v>
+      </c>
+      <c r="E37" t="n">
+        <v>260192</v>
+      </c>
+      <c r="F37" t="n">
+        <v>316.38</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>부산 금정구</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>13383336319</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5699</v>
+      </c>
+      <c r="E38" t="n">
+        <v>230938</v>
+      </c>
+      <c r="F38" t="n">
+        <v>246.78</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>부산 연제구</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>9240445542</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7504</v>
+      </c>
+      <c r="E39" t="n">
+        <v>200963</v>
+      </c>
+      <c r="F39" t="n">
+        <v>373.4</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>부산 수영구</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>7708613172</v>
+      </c>
+      <c r="D40" t="n">
+        <v>5817</v>
+      </c>
+      <c r="E40" t="n">
+        <v>190696</v>
+      </c>
+      <c r="F40" t="n">
+        <v>305.04</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>부산 사상구</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>13655807815</v>
+      </c>
+      <c r="D41" t="n">
+        <v>6818</v>
+      </c>
+      <c r="E41" t="n">
+        <v>231009</v>
+      </c>
+      <c r="F41" t="n">
+        <v>295.14</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>부산 기장군</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>17580280187</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7081</v>
+      </c>
+      <c r="E42" t="n">
+        <v>289966</v>
+      </c>
+      <c r="F42" t="n">
+        <v>244.2</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>대구 중구</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>8462788855</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6798</v>
+      </c>
+      <c r="E43" t="n">
+        <v>134040</v>
+      </c>
+      <c r="F43" t="n">
+        <v>507.16</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>대구 동구</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>15271568312</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9801</v>
+      </c>
+      <c r="E44" t="n">
+        <v>381760</v>
+      </c>
+      <c r="F44" t="n">
+        <v>256.73</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>대구 서구</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>13998084750</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5786</v>
+      </c>
+      <c r="E45" t="n">
+        <v>236800</v>
+      </c>
+      <c r="F45" t="n">
+        <v>244.34</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>대구 남구</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>13472050392</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4836</v>
+      </c>
+      <c r="E46" t="n">
+        <v>207796</v>
+      </c>
+      <c r="F46" t="n">
+        <v>232.73</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>대구 북구</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>23823768395</v>
+      </c>
+      <c r="D47" t="n">
+        <v>11444</v>
+      </c>
+      <c r="E47" t="n">
+        <v>372760</v>
+      </c>
+      <c r="F47" t="n">
+        <v>307.01</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>대구 수성구</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>15959516448</v>
+      </c>
+      <c r="D48" t="n">
+        <v>12263</v>
+      </c>
+      <c r="E48" t="n">
+        <v>339936</v>
+      </c>
+      <c r="F48" t="n">
+        <v>360.74</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>대구 달서구</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>18726761112</v>
+      </c>
+      <c r="D49" t="n">
+        <v>14586</v>
+      </c>
+      <c r="E49" t="n">
+        <v>444786</v>
+      </c>
+      <c r="F49" t="n">
+        <v>327.93</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>대구 달성군</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>24310021476</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5865</v>
+      </c>
+      <c r="E50" t="n">
+        <v>381200</v>
+      </c>
+      <c r="F50" t="n">
+        <v>153.86</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>대구 군위군</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>10226258799</v>
+      </c>
+      <c r="D51" t="n">
+        <v>486</v>
+      </c>
+      <c r="E51" t="n">
+        <v>160120</v>
+      </c>
+      <c r="F51" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>인천 중구</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>9839891186</v>
+      </c>
+      <c r="D52" t="n">
+        <v>8149</v>
+      </c>
+      <c r="E52" t="n">
+        <v>228622</v>
+      </c>
+      <c r="F52" t="n">
+        <v>356.44</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>인천 동구</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6252565890</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1151</v>
+      </c>
+      <c r="E53" t="n">
+        <v>136818</v>
+      </c>
+      <c r="F53" t="n">
+        <v>84.13</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>인천 미추홀구</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>27028127112</v>
+      </c>
+      <c r="D54" t="n">
+        <v>14899</v>
+      </c>
+      <c r="E54" t="n">
+        <v>415824</v>
+      </c>
+      <c r="F54" t="n">
+        <v>358.3</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>인천 연수구</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>21565619926</v>
+      </c>
+      <c r="D55" t="n">
+        <v>10567</v>
+      </c>
+      <c r="E55" t="n">
+        <v>334931</v>
+      </c>
+      <c r="F55" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>인천 남동구</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>25165591733</v>
+      </c>
+      <c r="D56" t="n">
+        <v>15832</v>
+      </c>
+      <c r="E56" t="n">
+        <v>482394</v>
+      </c>
+      <c r="F56" t="n">
+        <v>328.2</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>인천 부평구</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>23207356290</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16733</v>
+      </c>
+      <c r="E57" t="n">
+        <v>473548</v>
+      </c>
+      <c r="F57" t="n">
+        <v>353.35</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>인천 계양구</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>14378950019</v>
+      </c>
+      <c r="D58" t="n">
+        <v>8071</v>
+      </c>
+      <c r="E58" t="n">
+        <v>285869</v>
+      </c>
+      <c r="F58" t="n">
+        <v>282.33</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>인천 서구</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>31786996862</v>
+      </c>
+      <c r="D59" t="n">
+        <v>17333</v>
+      </c>
+      <c r="E59" t="n">
+        <v>520750</v>
+      </c>
+      <c r="F59" t="n">
+        <v>332.85</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>인천 강화군</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16238241239</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1666</v>
+      </c>
+      <c r="E60" t="n">
+        <v>267461</v>
+      </c>
+      <c r="F60" t="n">
+        <v>62.29</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>인천 옹진군</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>10357149852</v>
+      </c>
+      <c r="D61" t="n">
+        <v>396</v>
+      </c>
+      <c r="E61" t="n">
+        <v>175769</v>
+      </c>
+      <c r="F61" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>광주 동구</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>9912110377</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4236</v>
+      </c>
+      <c r="E62" t="n">
+        <v>89300</v>
+      </c>
+      <c r="F62" t="n">
+        <v>474.36</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>광주 서구</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>10481450039</v>
+      </c>
+      <c r="D63" t="n">
+        <v>11248</v>
+      </c>
+      <c r="E63" t="n">
+        <v>145298</v>
+      </c>
+      <c r="F63" t="n">
+        <v>774.13</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>광주 남구</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>10635759448</v>
+      </c>
+      <c r="D64" t="n">
+        <v>5470</v>
+      </c>
+      <c r="E64" t="n">
+        <v>132913</v>
+      </c>
+      <c r="F64" t="n">
+        <v>411.55</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>광주 북구</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>18452551333</v>
+      </c>
+      <c r="D65" t="n">
+        <v>12148</v>
+      </c>
+      <c r="E65" t="n">
+        <v>229716</v>
+      </c>
+      <c r="F65" t="n">
+        <v>528.83</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>광주 광산구</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>17781852707</v>
+      </c>
+      <c r="D66" t="n">
+        <v>13320</v>
+      </c>
+      <c r="E66" t="n">
+        <v>216167</v>
+      </c>
+      <c r="F66" t="n">
+        <v>616.1900000000001</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>대전 동구</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>11457659577</v>
+      </c>
+      <c r="D67" t="n">
+        <v>7396</v>
+      </c>
+      <c r="E67" t="n">
+        <v>159133</v>
+      </c>
+      <c r="F67" t="n">
+        <v>464.77</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>대전 중구</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>17118909320</v>
+      </c>
+      <c r="D68" t="n">
+        <v>8335</v>
+      </c>
+      <c r="E68" t="n">
+        <v>150916</v>
+      </c>
+      <c r="F68" t="n">
+        <v>552.29</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>대전 서구</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>17591131725</v>
+      </c>
+      <c r="D69" t="n">
+        <v>15941</v>
+      </c>
+      <c r="E69" t="n">
+        <v>219833</v>
+      </c>
+      <c r="F69" t="n">
+        <v>725.14</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>대전 유성구</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>13956768335</v>
+      </c>
+      <c r="D70" t="n">
+        <v>10011</v>
+      </c>
+      <c r="E70" t="n">
+        <v>174415</v>
+      </c>
+      <c r="F70" t="n">
+        <v>573.98</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>대전 대덕구</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>10819075718</v>
+      </c>
+      <c r="D71" t="n">
+        <v>5198</v>
+      </c>
+      <c r="E71" t="n">
+        <v>126133</v>
+      </c>
+      <c r="F71" t="n">
+        <v>412.1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>울산 중구</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>11234058498</v>
+      </c>
+      <c r="D72" t="n">
+        <v>5198</v>
+      </c>
+      <c r="E72" t="n">
+        <v>111675</v>
+      </c>
+      <c r="F72" t="n">
+        <v>465.46</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>울산 남구</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>12736696027</v>
+      </c>
+      <c r="D73" t="n">
+        <v>10822</v>
+      </c>
+      <c r="E73" t="n">
+        <v>148489</v>
+      </c>
+      <c r="F73" t="n">
+        <v>728.8099999999999</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>울산 동구</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>7113222760</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4173</v>
+      </c>
+      <c r="E74" t="n">
+        <v>88892</v>
+      </c>
+      <c r="F74" t="n">
+        <v>469.45</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>울산 북구</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9376689885</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4934</v>
+      </c>
+      <c r="E75" t="n">
+        <v>109785</v>
+      </c>
+      <c r="F75" t="n">
+        <v>449.42</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>산업단지 및 다문화/공업 밀집</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>울산 울주군</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>28313604635</v>
+      </c>
+      <c r="D76" t="n">
+        <v>5764</v>
+      </c>
+      <c r="E76" t="n">
+        <v>260171</v>
+      </c>
+      <c r="F76" t="n">
+        <v>221.55</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>세종시</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>38815087307</v>
+      </c>
+      <c r="D77" t="n">
+        <v>9707</v>
+      </c>
+      <c r="E77" t="n">
+        <v>365957</v>
+      </c>
+      <c r="F77" t="n">
+        <v>265.25</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>경기도 고양시</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>46280053405</v>
+      </c>
+      <c r="D78" t="n">
+        <v>28692</v>
+      </c>
+      <c r="E78" t="n">
+        <v>624355</v>
+      </c>
+      <c r="F78" t="n">
+        <v>459.55</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>대도시 중심 도심권 및 복합 상권</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>경기도 과천시</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>10812986918</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1769</v>
+      </c>
+      <c r="E79" t="n">
+        <v>99359</v>
+      </c>
+      <c r="F79" t="n">
+        <v>178.04</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>경기도 광명시</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>18770558529</v>
+      </c>
+      <c r="D80" t="n">
+        <v>7466</v>
+      </c>
+      <c r="E80" t="n">
+        <v>205093</v>
+      </c>
+      <c r="F80" t="n">
+        <v>364.03</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>경기도 광주시</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>32310074460</v>
+      </c>
+      <c r="D81" t="n">
+        <v>11929</v>
+      </c>
+      <c r="E81" t="n">
+        <v>276654</v>
+      </c>
+      <c r="F81" t="n">
+        <v>431.19</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>경기도 구리시</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>15853047857</v>
+      </c>
+      <c r="D82" t="n">
+        <v>5706</v>
+      </c>
+      <c r="E82" t="n">
+        <v>142824</v>
+      </c>
+      <c r="F82" t="n">
+        <v>399.51</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>경기도 군포시</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>13558065847</v>
+      </c>
+      <c r="D83" t="n">
+        <v>6434</v>
+      </c>
+      <c r="E83" t="n">
+        <v>168784</v>
+      </c>
+      <c r="F83" t="n">
+        <v>381.2</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>경기도 김포시</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>35601340788</v>
+      </c>
+      <c r="D84" t="n">
+        <v>16067</v>
+      </c>
+      <c r="E84" t="n">
+        <v>324021</v>
+      </c>
+      <c r="F84" t="n">
+        <v>495.86</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>경기도 남양주시</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>53034404574</v>
+      </c>
+      <c r="D85" t="n">
+        <v>18038</v>
+      </c>
+      <c r="E85" t="n">
+        <v>456463</v>
+      </c>
+      <c r="F85" t="n">
+        <v>395.17</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>경기도 동두천시</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>13771780461</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3389</v>
+      </c>
+      <c r="E86" t="n">
+        <v>119711</v>
+      </c>
+      <c r="F86" t="n">
+        <v>283.1</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>경기도 부천시</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>35736062217</v>
+      </c>
+      <c r="D87" t="n">
+        <v>26195</v>
+      </c>
+      <c r="E87" t="n">
+        <v>462816</v>
+      </c>
+      <c r="F87" t="n">
+        <v>565.99</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>경기도 성남시</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>55873172965</v>
+      </c>
+      <c r="D88" t="n">
+        <v>29286</v>
+      </c>
+      <c r="E88" t="n">
+        <v>702204</v>
+      </c>
+      <c r="F88" t="n">
+        <v>417.06</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>대도시 중심 도심권 및 복합 상권</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>경기도 수원시</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>65980415686</v>
+      </c>
+      <c r="D89" t="n">
+        <v>38826</v>
+      </c>
+      <c r="E89" t="n">
+        <v>640330</v>
+      </c>
+      <c r="F89" t="n">
+        <v>606.34</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>대도시 중심 도심권 및 복합 상권</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>33538907664</v>
+      </c>
+      <c r="D90" t="n">
+        <v>17507</v>
+      </c>
+      <c r="E90" t="n">
+        <v>342680</v>
+      </c>
+      <c r="F90" t="n">
+        <v>510.88</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>경기도 안산시</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>49091707502</v>
+      </c>
+      <c r="D91" t="n">
+        <v>25110</v>
+      </c>
+      <c r="E91" t="n">
+        <v>441214</v>
+      </c>
+      <c r="F91" t="n">
+        <v>569.11</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>산업단지 및 다문화/공업 밀집</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>경기도 안성시</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>25660092930</v>
+      </c>
+      <c r="D92" t="n">
+        <v>6745</v>
+      </c>
+      <c r="E92" t="n">
+        <v>241929</v>
+      </c>
+      <c r="F92" t="n">
+        <v>278.8</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>경기도 안양시</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>39781648683</v>
+      </c>
+      <c r="D93" t="n">
+        <v>13777</v>
+      </c>
+      <c r="E93" t="n">
+        <v>343244</v>
+      </c>
+      <c r="F93" t="n">
+        <v>401.38</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>경기도 양주시</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>27761776908</v>
+      </c>
+      <c r="D94" t="n">
+        <v>7565</v>
+      </c>
+      <c r="E94" t="n">
+        <v>237766</v>
+      </c>
+      <c r="F94" t="n">
+        <v>318.17</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>경기도 여주시</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>14946258937</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3754</v>
+      </c>
+      <c r="E95" t="n">
+        <v>181696</v>
+      </c>
+      <c r="F95" t="n">
+        <v>206.61</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>경기도 오산시</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>16992453248</v>
+      </c>
+      <c r="D96" t="n">
+        <v>8157</v>
+      </c>
+      <c r="E96" t="n">
+        <v>167334</v>
+      </c>
+      <c r="F96" t="n">
+        <v>487.47</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>경기도 용인시</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>72756052420</v>
+      </c>
+      <c r="D97" t="n">
+        <v>26603</v>
+      </c>
+      <c r="E97" t="n">
+        <v>651599</v>
+      </c>
+      <c r="F97" t="n">
+        <v>408.27</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>대도시 중심 도심권 및 복합 상권</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>경기도 의왕시</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>9140411456</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3267</v>
+      </c>
+      <c r="E98" t="n">
+        <v>121465</v>
+      </c>
+      <c r="F98" t="n">
+        <v>268.97</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>경기도 의정부시</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>26059518578</v>
+      </c>
+      <c r="D99" t="n">
+        <v>14099</v>
+      </c>
+      <c r="E99" t="n">
+        <v>286585</v>
+      </c>
+      <c r="F99" t="n">
+        <v>491.97</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>경기도 이천시</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>19134151216</v>
+      </c>
+      <c r="D100" t="n">
+        <v>6977</v>
+      </c>
+      <c r="E100" t="n">
+        <v>264761</v>
+      </c>
+      <c r="F100" t="n">
+        <v>263.52</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>경기도 파주시</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>43865153413</v>
+      </c>
+      <c r="D101" t="n">
+        <v>15373</v>
+      </c>
+      <c r="E101" t="n">
+        <v>394240</v>
+      </c>
+      <c r="F101" t="n">
+        <v>389.94</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>경기도 평택시</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>51070120641</v>
+      </c>
+      <c r="D102" t="n">
+        <v>25257</v>
+      </c>
+      <c r="E102" t="n">
+        <v>450652</v>
+      </c>
+      <c r="F102" t="n">
+        <v>560.45</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>경기도 포천시</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>21038445919</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4903</v>
+      </c>
+      <c r="E103" t="n">
+        <v>232370</v>
+      </c>
+      <c r="F103" t="n">
+        <v>211</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>경기도 하남시</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>14774126111</v>
+      </c>
+      <c r="D104" t="n">
+        <v>8988</v>
+      </c>
+      <c r="E104" t="n">
+        <v>203046</v>
+      </c>
+      <c r="F104" t="n">
+        <v>442.66</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>경기도 화성시</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>78387182207</v>
+      </c>
+      <c r="D105" t="n">
+        <v>29714</v>
+      </c>
+      <c r="E105" t="n">
+        <v>693056</v>
+      </c>
+      <c r="F105" t="n">
+        <v>428.74</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>경기도 연천군</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>11091400082</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1550</v>
+      </c>
+      <c r="E106" t="n">
+        <v>120667</v>
+      </c>
+      <c r="F106" t="n">
+        <v>128.45</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>경기도 가평군</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>11552128779</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2155</v>
+      </c>
+      <c r="E107" t="n">
+        <v>104076</v>
+      </c>
+      <c r="F107" t="n">
+        <v>207.06</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>경기도 양평군</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>17097251915</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3672</v>
+      </c>
+      <c r="E108" t="n">
+        <v>175752</v>
+      </c>
+      <c r="F108" t="n">
+        <v>208.93</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>강원도 강릉시</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>29561421157</v>
+      </c>
+      <c r="D109" t="n">
+        <v>5924</v>
+      </c>
+      <c r="E109" t="n">
+        <v>284370</v>
+      </c>
+      <c r="F109" t="n">
+        <v>208.32</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>강원도 동해시</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>11494840979</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2132</v>
+      </c>
+      <c r="E110" t="n">
+        <v>111555</v>
+      </c>
+      <c r="F110" t="n">
+        <v>191.12</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>강원도 삼척시</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>16909102446</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1727</v>
+      </c>
+      <c r="E111" t="n">
+        <v>152338</v>
+      </c>
+      <c r="F111" t="n">
+        <v>113.37</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>강원도 속초시</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>11375829497</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2992</v>
+      </c>
+      <c r="E112" t="n">
+        <v>97405</v>
+      </c>
+      <c r="F112" t="n">
+        <v>307.17</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>강원도 원주시</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>25315955893</v>
+      </c>
+      <c r="D113" t="n">
+        <v>11277</v>
+      </c>
+      <c r="E113" t="n">
+        <v>326224</v>
+      </c>
+      <c r="F113" t="n">
+        <v>345.68</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>강원도 춘천시</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>33535642977</v>
+      </c>
+      <c r="D114" t="n">
+        <v>8131</v>
+      </c>
+      <c r="E114" t="n">
+        <v>315171</v>
+      </c>
+      <c r="F114" t="n">
+        <v>257.99</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>강원도 태백시</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>11015827213</v>
+      </c>
+      <c r="D115" t="n">
+        <v>968</v>
+      </c>
+      <c r="E115" t="n">
+        <v>96931</v>
+      </c>
+      <c r="F115" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>강원도 홍천군</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>16017859435</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1938</v>
+      </c>
+      <c r="E116" t="n">
+        <v>159841</v>
+      </c>
+      <c r="F116" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>강원도 횡성군</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>9948924061</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1138</v>
+      </c>
+      <c r="E117" t="n">
+        <v>120945</v>
+      </c>
+      <c r="F117" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>강원도 영월군</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>10965619404</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1048</v>
+      </c>
+      <c r="E118" t="n">
+        <v>129211</v>
+      </c>
+      <c r="F118" t="n">
+        <v>81.11</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>강원도 평창군</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>9175449123</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1102</v>
+      </c>
+      <c r="E119" t="n">
+        <v>114663</v>
+      </c>
+      <c r="F119" t="n">
+        <v>96.11</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>강원도 정선군</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>13089947704</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1185</v>
+      </c>
+      <c r="E120" t="n">
+        <v>112942</v>
+      </c>
+      <c r="F120" t="n">
+        <v>104.92</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>강원도 철원군</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>13905648586</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1140</v>
+      </c>
+      <c r="E121" t="n">
+        <v>122588</v>
+      </c>
+      <c r="F121" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>강원도 화천군</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>6324118475</v>
+      </c>
+      <c r="D122" t="n">
+        <v>556</v>
+      </c>
+      <c r="E122" t="n">
+        <v>83448</v>
+      </c>
+      <c r="F122" t="n">
+        <v>66.63</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>강원도 양구군</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>6097843201</v>
+      </c>
+      <c r="D123" t="n">
+        <v>500</v>
+      </c>
+      <c r="E123" t="n">
+        <v>80808</v>
+      </c>
+      <c r="F123" t="n">
+        <v>61.88</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>강원도 인제군</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>9450827126</v>
+      </c>
+      <c r="D124" t="n">
+        <v>757</v>
+      </c>
+      <c r="E124" t="n">
+        <v>122798</v>
+      </c>
+      <c r="F124" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>강원도 고성군</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>8365521577</v>
+      </c>
+      <c r="D125" t="n">
+        <v>768</v>
+      </c>
+      <c r="E125" t="n">
+        <v>85473</v>
+      </c>
+      <c r="F125" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>강원도 양양군</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>7635517117</v>
+      </c>
+      <c r="D126" t="n">
+        <v>783</v>
+      </c>
+      <c r="E126" t="n">
+        <v>85809</v>
+      </c>
+      <c r="F126" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>충북 제천시</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>23816972922</v>
+      </c>
+      <c r="D127" t="n">
+        <v>3296</v>
+      </c>
+      <c r="E127" t="n">
+        <v>216767</v>
+      </c>
+      <c r="F127" t="n">
+        <v>152.05</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>충북 청주시</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>67995926219</v>
+      </c>
+      <c r="D128" t="n">
+        <v>26634</v>
+      </c>
+      <c r="E128" t="n">
+        <v>696143</v>
+      </c>
+      <c r="F128" t="n">
+        <v>382.59</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>대도시 중심 도심권 및 복합 상권</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>충북 충주시</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>28587556616</v>
+      </c>
+      <c r="D129" t="n">
+        <v>5493</v>
+      </c>
+      <c r="E129" t="n">
+        <v>277438</v>
+      </c>
+      <c r="F129" t="n">
+        <v>197.99</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>충북 보은군</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>7575521028</v>
+      </c>
+      <c r="D130" t="n">
+        <v>692</v>
+      </c>
+      <c r="E130" t="n">
+        <v>105189</v>
+      </c>
+      <c r="F130" t="n">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>충북 옥천군</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>8516382859</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1078</v>
+      </c>
+      <c r="E131" t="n">
+        <v>116873</v>
+      </c>
+      <c r="F131" t="n">
+        <v>92.23999999999999</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>충북 영동군</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>9930615529</v>
+      </c>
+      <c r="D132" t="n">
+        <v>804</v>
+      </c>
+      <c r="E132" t="n">
+        <v>102082</v>
+      </c>
+      <c r="F132" t="n">
+        <v>78.76000000000001</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>충북 증평군</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>4181406287</v>
+      </c>
+      <c r="D133" t="n">
+        <v>770</v>
+      </c>
+      <c r="E133" t="n">
+        <v>58070</v>
+      </c>
+      <c r="F133" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>충북 진천군</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>10725096328</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2740</v>
+      </c>
+      <c r="E134" t="n">
+        <v>130116</v>
+      </c>
+      <c r="F134" t="n">
+        <v>210.58</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>충북 괴산군</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>11731139407</v>
+      </c>
+      <c r="D135" t="n">
+        <v>977</v>
+      </c>
+      <c r="E135" t="n">
+        <v>105689</v>
+      </c>
+      <c r="F135" t="n">
+        <v>92.44</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>충북 음성군</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>13829988970</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3796</v>
+      </c>
+      <c r="E136" t="n">
+        <v>163654</v>
+      </c>
+      <c r="F136" t="n">
+        <v>231.95</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>충북 단양군</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>10159554955</v>
+      </c>
+      <c r="D137" t="n">
+        <v>660</v>
+      </c>
+      <c r="E137" t="n">
+        <v>89235</v>
+      </c>
+      <c r="F137" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>충남 계룡시</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>6186589916</v>
+      </c>
+      <c r="D138" t="n">
+        <v>647</v>
+      </c>
+      <c r="E138" t="n">
+        <v>52881</v>
+      </c>
+      <c r="F138" t="n">
+        <v>122.35</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>충남 공주시</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>18859087316</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2747</v>
+      </c>
+      <c r="E139" t="n">
+        <v>207400</v>
+      </c>
+      <c r="F139" t="n">
+        <v>132.45</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>충남 논산시</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>24900132950</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3607</v>
+      </c>
+      <c r="E140" t="n">
+        <v>219513</v>
+      </c>
+      <c r="F140" t="n">
+        <v>164.32</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>충남 당진시</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>20720156752</v>
+      </c>
+      <c r="D141" t="n">
+        <v>5725</v>
+      </c>
+      <c r="E141" t="n">
+        <v>234887</v>
+      </c>
+      <c r="F141" t="n">
+        <v>243.73</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>충남 보령시</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>19962886106</v>
+      </c>
+      <c r="D142" t="n">
+        <v>2916</v>
+      </c>
+      <c r="E142" t="n">
+        <v>192371</v>
+      </c>
+      <c r="F142" t="n">
+        <v>151.58</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>충남 서산시</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>28339914350</v>
+      </c>
+      <c r="D143" t="n">
+        <v>5408</v>
+      </c>
+      <c r="E143" t="n">
+        <v>250077</v>
+      </c>
+      <c r="F143" t="n">
+        <v>216.25</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>충남 아산시</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>31000959740</v>
+      </c>
+      <c r="D144" t="n">
+        <v>10309</v>
+      </c>
+      <c r="E144" t="n">
+        <v>361422</v>
+      </c>
+      <c r="F144" t="n">
+        <v>285.23</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>충남 천안시</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>38079490344</v>
+      </c>
+      <c r="D145" t="n">
+        <v>24978</v>
+      </c>
+      <c r="E145" t="n">
+        <v>466666</v>
+      </c>
+      <c r="F145" t="n">
+        <v>535.24</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>대도시 중심 도심권 및 복합 상권</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>충남 금산군</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>10959097966</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1108</v>
+      </c>
+      <c r="E146" t="n">
+        <v>150280</v>
+      </c>
+      <c r="F146" t="n">
+        <v>73.73</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>충남 부여군</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>12039140075</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1134</v>
+      </c>
+      <c r="E147" t="n">
+        <v>155400</v>
+      </c>
+      <c r="F147" t="n">
+        <v>72.97</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>충남 서천군</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>12988121303</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1191</v>
+      </c>
+      <c r="E148" t="n">
+        <v>153692</v>
+      </c>
+      <c r="F148" t="n">
+        <v>77.48999999999999</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>충남 청양군</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>9465340794</v>
+      </c>
+      <c r="D149" t="n">
+        <v>687</v>
+      </c>
+      <c r="E149" t="n">
+        <v>121555</v>
+      </c>
+      <c r="F149" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>충남 예산군</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>14952393389</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2063</v>
+      </c>
+      <c r="E150" t="n">
+        <v>183242</v>
+      </c>
+      <c r="F150" t="n">
+        <v>112.58</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>충남 태안군</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>12405974226</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1963</v>
+      </c>
+      <c r="E151" t="n">
+        <v>146183</v>
+      </c>
+      <c r="F151" t="n">
+        <v>134.28</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>충남 홍성군</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>16801405154</v>
+      </c>
+      <c r="D152" t="n">
+        <v>2710</v>
+      </c>
+      <c r="E152" t="n">
+        <v>172711</v>
+      </c>
+      <c r="F152" t="n">
+        <v>156.91</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>전북 군산시</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>26719372531</v>
+      </c>
+      <c r="D153" t="n">
+        <v>8513</v>
+      </c>
+      <c r="E153" t="n">
+        <v>327447</v>
+      </c>
+      <c r="F153" t="n">
+        <v>259.98</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>전북 김제시</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>16470562055</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1978</v>
+      </c>
+      <c r="E154" t="n">
+        <v>228757</v>
+      </c>
+      <c r="F154" t="n">
+        <v>86.47</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>전북 남원시</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>18769964377</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1728</v>
+      </c>
+      <c r="E155" t="n">
+        <v>206419</v>
+      </c>
+      <c r="F155" t="n">
+        <v>83.70999999999999</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>전북 익산시</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>38325512685</v>
+      </c>
+      <c r="D156" t="n">
+        <v>8043</v>
+      </c>
+      <c r="E156" t="n">
+        <v>367406</v>
+      </c>
+      <c r="F156" t="n">
+        <v>218.91</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>전북 전주시</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>39363603053</v>
+      </c>
+      <c r="D157" t="n">
+        <v>19767</v>
+      </c>
+      <c r="E157" t="n">
+        <v>544190</v>
+      </c>
+      <c r="F157" t="n">
+        <v>363.24</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>대도시 중심 도심권 및 복합 상권</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>전북 정읍시</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>26484460425</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2548</v>
+      </c>
+      <c r="E158" t="n">
+        <v>238605</v>
+      </c>
+      <c r="F158" t="n">
+        <v>106.79</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>전북 완주군</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>20695978564</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2084</v>
+      </c>
+      <c r="E159" t="n">
+        <v>188866</v>
+      </c>
+      <c r="F159" t="n">
+        <v>110.34</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>전북 고창군</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>19254496226</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1170</v>
+      </c>
+      <c r="E160" t="n">
+        <v>184582</v>
+      </c>
+      <c r="F160" t="n">
+        <v>63.39</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>전북 부안군</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>12605820752</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1116</v>
+      </c>
+      <c r="E161" t="n">
+        <v>172993</v>
+      </c>
+      <c r="F161" t="n">
+        <v>64.51000000000001</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>전북 임실군</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>7738551791</v>
+      </c>
+      <c r="D162" t="n">
+        <v>482</v>
+      </c>
+      <c r="E162" t="n">
+        <v>106353</v>
+      </c>
+      <c r="F162" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>전북 순창군</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>9335125162</v>
+      </c>
+      <c r="D163" t="n">
+        <v>498</v>
+      </c>
+      <c r="E163" t="n">
+        <v>113253</v>
+      </c>
+      <c r="F163" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>전북 진안군</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>8280871272</v>
+      </c>
+      <c r="D164" t="n">
+        <v>556</v>
+      </c>
+      <c r="E164" t="n">
+        <v>109267</v>
+      </c>
+      <c r="F164" t="n">
+        <v>50.88</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>전북 무주군</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>7684843948</v>
+      </c>
+      <c r="D165" t="n">
+        <v>625</v>
+      </c>
+      <c r="E165" t="n">
+        <v>93800</v>
+      </c>
+      <c r="F165" t="n">
+        <v>66.63</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>전북 장수군</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>10882059974</v>
+      </c>
+      <c r="D166" t="n">
+        <v>494</v>
+      </c>
+      <c r="E166" t="n">
+        <v>94461</v>
+      </c>
+      <c r="F166" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>전남 광양시</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>15359565508</v>
+      </c>
+      <c r="D167" t="n">
+        <v>4172</v>
+      </c>
+      <c r="E167" t="n">
+        <v>212920</v>
+      </c>
+      <c r="F167" t="n">
+        <v>195.94</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>전남 나주시</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>24024037592</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2927</v>
+      </c>
+      <c r="E168" t="n">
+        <v>205863</v>
+      </c>
+      <c r="F168" t="n">
+        <v>142.18</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>전남 목포시</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>14789258613</v>
+      </c>
+      <c r="D169" t="n">
+        <v>8437</v>
+      </c>
+      <c r="E169" t="n">
+        <v>202958</v>
+      </c>
+      <c r="F169" t="n">
+        <v>415.7</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>전남 순천시</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>21178619010</v>
+      </c>
+      <c r="D170" t="n">
+        <v>7490</v>
+      </c>
+      <c r="E170" t="n">
+        <v>285716</v>
+      </c>
+      <c r="F170" t="n">
+        <v>262.15</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>전남 여수시</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>25750133852</v>
+      </c>
+      <c r="D171" t="n">
+        <v>7694</v>
+      </c>
+      <c r="E171" t="n">
+        <v>300205</v>
+      </c>
+      <c r="F171" t="n">
+        <v>256.29</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>전남 담양군</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>10884505233</v>
+      </c>
+      <c r="D172" t="n">
+        <v>906</v>
+      </c>
+      <c r="E172" t="n">
+        <v>115179</v>
+      </c>
+      <c r="F172" t="n">
+        <v>78.66</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>전남 곡성군</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>10171728017</v>
+      </c>
+      <c r="D173" t="n">
+        <v>601</v>
+      </c>
+      <c r="E173" t="n">
+        <v>97510</v>
+      </c>
+      <c r="F173" t="n">
+        <v>61.63</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>전남 구례군</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>5472407180</v>
+      </c>
+      <c r="D174" t="n">
+        <v>600</v>
+      </c>
+      <c r="E174" t="n">
+        <v>75722</v>
+      </c>
+      <c r="F174" t="n">
+        <v>79.23999999999999</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>전남 고흥군</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>22953622924</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E175" t="n">
+        <v>196587</v>
+      </c>
+      <c r="F175" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>전남 보성군</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>10891139245</v>
+      </c>
+      <c r="D176" t="n">
+        <v>947</v>
+      </c>
+      <c r="E176" t="n">
+        <v>126973</v>
+      </c>
+      <c r="F176" t="n">
+        <v>74.58</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>전남 화순군</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>15866823021</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1431</v>
+      </c>
+      <c r="E177" t="n">
+        <v>139878</v>
+      </c>
+      <c r="F177" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>전남 장흥군</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>11660011797</v>
+      </c>
+      <c r="D178" t="n">
+        <v>987</v>
+      </c>
+      <c r="E178" t="n">
+        <v>115910</v>
+      </c>
+      <c r="F178" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>전남 강진군</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>11084299249</v>
+      </c>
+      <c r="D179" t="n">
+        <v>831</v>
+      </c>
+      <c r="E179" t="n">
+        <v>104505</v>
+      </c>
+      <c r="F179" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>전남 해남군</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>14551072115</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1577</v>
+      </c>
+      <c r="E180" t="n">
+        <v>195851</v>
+      </c>
+      <c r="F180" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>전남 영암군</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>11418263098</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1334</v>
+      </c>
+      <c r="E181" t="n">
+        <v>144037</v>
+      </c>
+      <c r="F181" t="n">
+        <v>92.62</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>전남 무안군</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>12571989176</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1908</v>
+      </c>
+      <c r="E182" t="n">
+        <v>131925</v>
+      </c>
+      <c r="F182" t="n">
+        <v>144.63</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>전남 함평군</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>12738686893</v>
+      </c>
+      <c r="D183" t="n">
+        <v>713</v>
+      </c>
+      <c r="E183" t="n">
+        <v>109222</v>
+      </c>
+      <c r="F183" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>전남 영광군</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>10054569049</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1201</v>
+      </c>
+      <c r="E184" t="n">
+        <v>133243</v>
+      </c>
+      <c r="F184" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>전남 장성군</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>9154989295</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1053</v>
+      </c>
+      <c r="E185" t="n">
+        <v>125130</v>
+      </c>
+      <c r="F185" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>전남 완도군</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>15413605349</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1239</v>
+      </c>
+      <c r="E186" t="n">
+        <v>132157</v>
+      </c>
+      <c r="F186" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>전남 진도군</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>6827810488</v>
+      </c>
+      <c r="D187" t="n">
+        <v>873</v>
+      </c>
+      <c r="E187" t="n">
+        <v>94823</v>
+      </c>
+      <c r="F187" t="n">
+        <v>92.06999999999999</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>전남 신안군</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>16731390896</v>
+      </c>
+      <c r="D188" t="n">
+        <v>564</v>
+      </c>
+      <c r="E188" t="n">
+        <v>147641</v>
+      </c>
+      <c r="F188" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>경북 경산시</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>29036567692</v>
+      </c>
+      <c r="D189" t="n">
+        <v>8565</v>
+      </c>
+      <c r="E189" t="n">
+        <v>272888</v>
+      </c>
+      <c r="F189" t="n">
+        <v>313.87</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>경북 경주시</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>28000957285</v>
+      </c>
+      <c r="D190" t="n">
+        <v>7885</v>
+      </c>
+      <c r="E190" t="n">
+        <v>384266</v>
+      </c>
+      <c r="F190" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>경북 구미시</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>34936579110</v>
+      </c>
+      <c r="D191" t="n">
+        <v>11979</v>
+      </c>
+      <c r="E191" t="n">
+        <v>394333</v>
+      </c>
+      <c r="F191" t="n">
+        <v>303.78</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>산업단지 및 다문화/공업 밀집</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>경북 김천시</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>32196821169</v>
+      </c>
+      <c r="D192" t="n">
+        <v>3426</v>
+      </c>
+      <c r="E192" t="n">
+        <v>284111</v>
+      </c>
+      <c r="F192" t="n">
+        <v>120.59</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>경북 문경시</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>23834872496</v>
+      </c>
+      <c r="D193" t="n">
+        <v>1755</v>
+      </c>
+      <c r="E193" t="n">
+        <v>207333</v>
+      </c>
+      <c r="F193" t="n">
+        <v>84.65000000000001</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>경북 상주시</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>28577984093</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2124</v>
+      </c>
+      <c r="E194" t="n">
+        <v>252177</v>
+      </c>
+      <c r="F194" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>경북 안동시</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>30528778308</v>
+      </c>
+      <c r="D195" t="n">
+        <v>4048</v>
+      </c>
+      <c r="E195" t="n">
+        <v>325111</v>
+      </c>
+      <c r="F195" t="n">
+        <v>124.51</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>경북 영주시</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>21576791669</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2191</v>
+      </c>
+      <c r="E196" t="n">
+        <v>221800</v>
+      </c>
+      <c r="F196" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>경북 영천시</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>21288852519</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2729</v>
+      </c>
+      <c r="E197" t="n">
+        <v>217955</v>
+      </c>
+      <c r="F197" t="n">
+        <v>125.21</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>경북 포항시</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>43509191594</v>
+      </c>
+      <c r="D198" t="n">
+        <v>13539</v>
+      </c>
+      <c r="E198" t="n">
+        <v>565333</v>
+      </c>
+      <c r="F198" t="n">
+        <v>239.49</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>산업단지 및 다문화/공업 밀집</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>경북 의성군</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>11206957634</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1060</v>
+      </c>
+      <c r="E199" t="n">
+        <v>148515</v>
+      </c>
+      <c r="F199" t="n">
+        <v>71.37</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>경북 청송군</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>9722345218</v>
+      </c>
+      <c r="D200" t="n">
+        <v>604</v>
+      </c>
+      <c r="E200" t="n">
+        <v>98939</v>
+      </c>
+      <c r="F200" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>경북 영양군</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>6851304438</v>
+      </c>
+      <c r="D201" t="n">
+        <v>307</v>
+      </c>
+      <c r="E201" t="n">
+        <v>83288</v>
+      </c>
+      <c r="F201" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>경북 영덕군</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>9466746813</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1039</v>
+      </c>
+      <c r="E202" t="n">
+        <v>130992</v>
+      </c>
+      <c r="F202" t="n">
+        <v>79.31999999999999</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>경북 청도군</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>11247692134</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1004</v>
+      </c>
+      <c r="E203" t="n">
+        <v>126954</v>
+      </c>
+      <c r="F203" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>경북 고령군</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>7014890310</v>
+      </c>
+      <c r="D204" t="n">
+        <v>659</v>
+      </c>
+      <c r="E204" t="n">
+        <v>97404</v>
+      </c>
+      <c r="F204" t="n">
+        <v>67.66</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>경북 성주군</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>9288995302</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1191</v>
+      </c>
+      <c r="E205" t="n">
+        <v>126000</v>
+      </c>
+      <c r="F205" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>경북 칠곡군</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>11040844651</v>
+      </c>
+      <c r="D206" t="n">
+        <v>3358</v>
+      </c>
+      <c r="E206" t="n">
+        <v>153333</v>
+      </c>
+      <c r="F206" t="n">
+        <v>219</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>경북 예천군</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>11037210314</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1243</v>
+      </c>
+      <c r="E207" t="n">
+        <v>141741</v>
+      </c>
+      <c r="F207" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>경북 봉화군</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>11476815158</v>
+      </c>
+      <c r="D208" t="n">
+        <v>527</v>
+      </c>
+      <c r="E208" t="n">
+        <v>114088</v>
+      </c>
+      <c r="F208" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>경북 울진군</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>9472028988</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1142</v>
+      </c>
+      <c r="E209" t="n">
+        <v>131555</v>
+      </c>
+      <c r="F209" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>경북 울릉군</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>4107701517</v>
+      </c>
+      <c r="D210" t="n">
+        <v>189</v>
+      </c>
+      <c r="E210" t="n">
+        <v>46666</v>
+      </c>
+      <c r="F210" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>경남 거제시</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>27260448100</v>
+      </c>
+      <c r="D211" t="n">
+        <v>7930</v>
+      </c>
+      <c r="E211" t="n">
+        <v>257017</v>
+      </c>
+      <c r="F211" t="n">
+        <v>308.54</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>경남 김해시</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>37261768197</v>
+      </c>
+      <c r="D212" t="n">
+        <v>17343</v>
+      </c>
+      <c r="E212" t="n">
+        <v>418757</v>
+      </c>
+      <c r="F212" t="n">
+        <v>414.15</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>경남 밀양시</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>25212065205</v>
+      </c>
+      <c r="D213" t="n">
+        <v>3270</v>
+      </c>
+      <c r="E213" t="n">
+        <v>219635</v>
+      </c>
+      <c r="F213" t="n">
+        <v>148.88</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>경남 사천시</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>15632220893</v>
+      </c>
+      <c r="D214" t="n">
+        <v>3294</v>
+      </c>
+      <c r="E214" t="n">
+        <v>189649</v>
+      </c>
+      <c r="F214" t="n">
+        <v>173.69</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>경남 양산시</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>36105704295</v>
+      </c>
+      <c r="D215" t="n">
+        <v>9212</v>
+      </c>
+      <c r="E215" t="n">
+        <v>339325</v>
+      </c>
+      <c r="F215" t="n">
+        <v>271.48</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>경남 진주시</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>24328919376</v>
+      </c>
+      <c r="D216" t="n">
+        <v>11911</v>
+      </c>
+      <c r="E216" t="n">
+        <v>330008</v>
+      </c>
+      <c r="F216" t="n">
+        <v>360.93</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>경남 창원시</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>57978047481</v>
+      </c>
+      <c r="D217" t="n">
+        <v>29588</v>
+      </c>
+      <c r="E217" t="n">
+        <v>731375</v>
+      </c>
+      <c r="F217" t="n">
+        <v>404.55</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>대도시 중심 도심권 및 복합 상권</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>경남 통영시</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>13804759748</v>
+      </c>
+      <c r="D218" t="n">
+        <v>4619</v>
+      </c>
+      <c r="E218" t="n">
+        <v>171855</v>
+      </c>
+      <c r="F218" t="n">
+        <v>268.77</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>경남 함안군</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>16330155203</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1508</v>
+      </c>
+      <c r="E219" t="n">
+        <v>152280</v>
+      </c>
+      <c r="F219" t="n">
+        <v>99.03</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>경남 거창군</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>19259000699</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1477</v>
+      </c>
+      <c r="E220" t="n">
+        <v>165128</v>
+      </c>
+      <c r="F220" t="n">
+        <v>89.45</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>경남 창녕군</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>14675129119</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1535</v>
+      </c>
+      <c r="E221" t="n">
+        <v>145882</v>
+      </c>
+      <c r="F221" t="n">
+        <v>105.22</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>경남 고성군</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>13845488638</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1314</v>
+      </c>
+      <c r="E222" t="n">
+        <v>137635</v>
+      </c>
+      <c r="F222" t="n">
+        <v>95.47</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>경남 하동군</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>9354472819</v>
+      </c>
+      <c r="D223" t="n">
+        <v>885</v>
+      </c>
+      <c r="E223" t="n">
+        <v>128072</v>
+      </c>
+      <c r="F223" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>경남 합천군</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>14620013865</v>
+      </c>
+      <c r="D224" t="n">
+        <v>964</v>
+      </c>
+      <c r="E224" t="n">
+        <v>159743</v>
+      </c>
+      <c r="F224" t="n">
+        <v>60.35</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>경남 남해군</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>12615771643</v>
+      </c>
+      <c r="D225" t="n">
+        <v>896</v>
+      </c>
+      <c r="E225" t="n">
+        <v>118944</v>
+      </c>
+      <c r="F225" t="n">
+        <v>75.33</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>경남 함양군</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>12015909025</v>
+      </c>
+      <c r="D226" t="n">
+        <v>943</v>
+      </c>
+      <c r="E226" t="n">
+        <v>135037</v>
+      </c>
+      <c r="F226" t="n">
+        <v>69.83</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>경남 산청군</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>11310370633</v>
+      </c>
+      <c r="D227" t="n">
+        <v>696</v>
+      </c>
+      <c r="E227" t="n">
+        <v>131861</v>
+      </c>
+      <c r="F227" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>경남 의령군</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>9609090167</v>
+      </c>
+      <c r="D228" t="n">
+        <v>669</v>
+      </c>
+      <c r="E228" t="n">
+        <v>94981</v>
+      </c>
+      <c r="F228" t="n">
+        <v>70.44</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>전원형 농어촌 및 고령 주거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>제주 서귀포시</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>44168492474</v>
+      </c>
+      <c r="D229" t="n">
+        <v>6995</v>
+      </c>
+      <c r="E229" t="n">
+        <v>383405</v>
+      </c>
+      <c r="F229" t="n">
+        <v>182.44</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>제주 제주시</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>114264422703</v>
+      </c>
+      <c r="D230" t="n">
+        <v>20916</v>
+      </c>
+      <c r="E230" t="n">
+        <v>985898</v>
+      </c>
+      <c r="F230" t="n">
+        <v>212.15</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>주거 밀집 베드타운</t>
         </is>
       </c>
     </row>

--- a/crime_data.xlsx
+++ b/crime_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G230"/>
+  <dimension ref="A1:I230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,16 @@
           <t>특이사항</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>위도</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>경도</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +503,12 @@
           <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>37.573</v>
+      </c>
+      <c r="I2" t="n">
+        <v>126.9794</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +538,12 @@
           <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>37.5636</v>
+      </c>
+      <c r="I3" t="n">
+        <v>126.9975</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +573,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>37.5326</v>
+      </c>
+      <c r="I4" t="n">
+        <v>126.99</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +608,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>37.5633</v>
+      </c>
+      <c r="I5" t="n">
+        <v>127.0371</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +643,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>37.5385</v>
+      </c>
+      <c r="I6" t="n">
+        <v>127.0822</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,6 +678,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>37.5744</v>
+      </c>
+      <c r="I7" t="n">
+        <v>127.04</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -667,6 +713,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H8" t="n">
+        <v>37.6065</v>
+      </c>
+      <c r="I8" t="n">
+        <v>127.0927</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -696,6 +748,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H9" t="n">
+        <v>37.5891</v>
+      </c>
+      <c r="I9" t="n">
+        <v>127.0182</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -725,6 +783,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H10" t="n">
+        <v>37.6396</v>
+      </c>
+      <c r="I10" t="n">
+        <v>127.0257</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -754,6 +818,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H11" t="n">
+        <v>37.6688</v>
+      </c>
+      <c r="I11" t="n">
+        <v>127.0471</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -783,6 +853,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H12" t="n">
+        <v>37.6542</v>
+      </c>
+      <c r="I12" t="n">
+        <v>127.0568</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -812,6 +888,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H13" t="n">
+        <v>37.6027</v>
+      </c>
+      <c r="I13" t="n">
+        <v>126.9291</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -841,6 +923,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H14" t="n">
+        <v>37.5791</v>
+      </c>
+      <c r="I14" t="n">
+        <v>126.9368</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -870,6 +958,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H15" t="n">
+        <v>37.5662</v>
+      </c>
+      <c r="I15" t="n">
+        <v>126.9016</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -899,6 +993,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H16" t="n">
+        <v>37.5169</v>
+      </c>
+      <c r="I16" t="n">
+        <v>126.866</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -928,6 +1028,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H17" t="n">
+        <v>37.5509</v>
+      </c>
+      <c r="I17" t="n">
+        <v>126.8497</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -957,6 +1063,12 @@
           <t>산업단지 및 다문화/공업 밀집</t>
         </is>
       </c>
+      <c r="H18" t="n">
+        <v>37.4954</v>
+      </c>
+      <c r="I18" t="n">
+        <v>126.8874</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -986,6 +1098,12 @@
           <t>산업단지 및 다문화/공업 밀집</t>
         </is>
       </c>
+      <c r="H19" t="n">
+        <v>37.4568</v>
+      </c>
+      <c r="I19" t="n">
+        <v>126.8954</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1015,6 +1133,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H20" t="n">
+        <v>37.5264</v>
+      </c>
+      <c r="I20" t="n">
+        <v>126.8962</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1044,6 +1168,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H21" t="n">
+        <v>37.5124</v>
+      </c>
+      <c r="I21" t="n">
+        <v>126.9393</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1073,6 +1203,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H22" t="n">
+        <v>37.4784</v>
+      </c>
+      <c r="I22" t="n">
+        <v>126.9516</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1102,6 +1238,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H23" t="n">
+        <v>37.4837</v>
+      </c>
+      <c r="I23" t="n">
+        <v>127.0324</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1131,6 +1273,12 @@
           <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
+      <c r="H24" t="n">
+        <v>37.5172</v>
+      </c>
+      <c r="I24" t="n">
+        <v>127.0473</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1160,6 +1308,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H25" t="n">
+        <v>37.5145</v>
+      </c>
+      <c r="I25" t="n">
+        <v>127.1066</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1189,6 +1343,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H26" t="n">
+        <v>37.5301</v>
+      </c>
+      <c r="I26" t="n">
+        <v>127.1238</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1218,6 +1378,12 @@
           <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
+      <c r="H27" t="n">
+        <v>35.1062</v>
+      </c>
+      <c r="I27" t="n">
+        <v>129.0324</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1247,6 +1413,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H28" t="n">
+        <v>35.0979</v>
+      </c>
+      <c r="I28" t="n">
+        <v>129.0244</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1276,6 +1448,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H29" t="n">
+        <v>35.1293</v>
+      </c>
+      <c r="I29" t="n">
+        <v>129.0454</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1305,6 +1483,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H30" t="n">
+        <v>35.0912</v>
+      </c>
+      <c r="I30" t="n">
+        <v>129.0679</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1334,6 +1518,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H31" t="n">
+        <v>35.0746</v>
+      </c>
+      <c r="I31" t="n">
+        <v>128.7156</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1363,6 +1553,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H32" t="n">
+        <v>35.2048</v>
+      </c>
+      <c r="I32" t="n">
+        <v>129.0836</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1392,6 +1588,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H33" t="n">
+        <v>35.1365</v>
+      </c>
+      <c r="I33" t="n">
+        <v>129.0842</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1421,6 +1623,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H34" t="n">
+        <v>35.1972</v>
+      </c>
+      <c r="I34" t="n">
+        <v>128.9902</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1450,6 +1658,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H35" t="n">
+        <v>35.2122</v>
+      </c>
+      <c r="I35" t="n">
+        <v>128.9806</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1479,6 +1693,12 @@
           <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
+      <c r="H36" t="n">
+        <v>35.1631</v>
+      </c>
+      <c r="I36" t="n">
+        <v>129.1636</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1508,6 +1728,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H37" t="n">
+        <v>35.1045</v>
+      </c>
+      <c r="I37" t="n">
+        <v>128.9748</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1537,6 +1763,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H38" t="n">
+        <v>35.243</v>
+      </c>
+      <c r="I38" t="n">
+        <v>129.0921</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1566,6 +1798,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H39" t="n">
+        <v>35.1765</v>
+      </c>
+      <c r="I39" t="n">
+        <v>129.0797</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1595,6 +1833,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H40" t="n">
+        <v>35.1456</v>
+      </c>
+      <c r="I40" t="n">
+        <v>129.1132</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1624,6 +1868,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H41" t="n">
+        <v>35.1526</v>
+      </c>
+      <c r="I41" t="n">
+        <v>128.9912</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1653,6 +1903,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H42" t="n">
+        <v>35.2445</v>
+      </c>
+      <c r="I42" t="n">
+        <v>129.2224</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1682,6 +1938,12 @@
           <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
+      <c r="H43" t="n">
+        <v>35.8694</v>
+      </c>
+      <c r="I43" t="n">
+        <v>128.6062</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1711,6 +1973,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H44" t="n">
+        <v>35.8866</v>
+      </c>
+      <c r="I44" t="n">
+        <v>128.6358</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1740,6 +2008,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H45" t="n">
+        <v>35.8719</v>
+      </c>
+      <c r="I45" t="n">
+        <v>128.5591</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1769,6 +2043,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H46" t="n">
+        <v>35.8459</v>
+      </c>
+      <c r="I46" t="n">
+        <v>128.5974</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1798,6 +2078,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H47" t="n">
+        <v>35.8857</v>
+      </c>
+      <c r="I47" t="n">
+        <v>128.5828</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1827,6 +2113,12 @@
           <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
+      <c r="H48" t="n">
+        <v>35.8583</v>
+      </c>
+      <c r="I48" t="n">
+        <v>128.6306</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1856,6 +2148,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H49" t="n">
+        <v>35.8298</v>
+      </c>
+      <c r="I49" t="n">
+        <v>128.5327</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1885,6 +2183,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H50" t="n">
+        <v>35.7746</v>
+      </c>
+      <c r="I50" t="n">
+        <v>128.4313</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1914,6 +2218,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H51" t="n">
+        <v>36.2428</v>
+      </c>
+      <c r="I51" t="n">
+        <v>128.5728</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1943,6 +2253,12 @@
           <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
+      <c r="H52" t="n">
+        <v>37.4738</v>
+      </c>
+      <c r="I52" t="n">
+        <v>126.6216</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1972,6 +2288,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H53" t="n">
+        <v>37.4738</v>
+      </c>
+      <c r="I53" t="n">
+        <v>126.6432</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2001,6 +2323,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H54" t="n">
+        <v>37.4636</v>
+      </c>
+      <c r="I54" t="n">
+        <v>126.6502</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2030,6 +2358,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H55" t="n">
+        <v>37.4101</v>
+      </c>
+      <c r="I55" t="n">
+        <v>126.6783</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2059,6 +2393,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H56" t="n">
+        <v>37.447</v>
+      </c>
+      <c r="I56" t="n">
+        <v>126.7314</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2088,6 +2428,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H57" t="n">
+        <v>37.507</v>
+      </c>
+      <c r="I57" t="n">
+        <v>126.7218</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2117,6 +2463,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H58" t="n">
+        <v>37.5374</v>
+      </c>
+      <c r="I58" t="n">
+        <v>126.7377</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2146,6 +2498,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H59" t="n">
+        <v>37.5454</v>
+      </c>
+      <c r="I59" t="n">
+        <v>126.676</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2175,6 +2533,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H60" t="n">
+        <v>37.7465</v>
+      </c>
+      <c r="I60" t="n">
+        <v>126.488</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2204,6 +2568,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H61" t="n">
+        <v>37.4465</v>
+      </c>
+      <c r="I61" t="n">
+        <v>126.6368</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2233,6 +2603,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H62" t="n">
+        <v>35.146</v>
+      </c>
+      <c r="I62" t="n">
+        <v>126.9232</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2262,6 +2638,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H63" t="n">
+        <v>35.152</v>
+      </c>
+      <c r="I63" t="n">
+        <v>126.8897</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2291,6 +2673,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H64" t="n">
+        <v>35.1329</v>
+      </c>
+      <c r="I64" t="n">
+        <v>126.9025</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2320,6 +2708,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H65" t="n">
+        <v>35.1741</v>
+      </c>
+      <c r="I65" t="n">
+        <v>126.9121</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2349,6 +2743,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H66" t="n">
+        <v>35.1396</v>
+      </c>
+      <c r="I66" t="n">
+        <v>126.7937</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2378,6 +2778,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H67" t="n">
+        <v>36.312</v>
+      </c>
+      <c r="I67" t="n">
+        <v>127.455</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2407,6 +2813,12 @@
           <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
+      <c r="H68" t="n">
+        <v>36.3259</v>
+      </c>
+      <c r="I68" t="n">
+        <v>127.4214</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2436,6 +2848,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H69" t="n">
+        <v>36.3553</v>
+      </c>
+      <c r="I69" t="n">
+        <v>127.3837</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2465,6 +2883,12 @@
           <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
+      <c r="H70" t="n">
+        <v>36.3623</v>
+      </c>
+      <c r="I70" t="n">
+        <v>127.3564</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2494,6 +2918,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H71" t="n">
+        <v>36.3467</v>
+      </c>
+      <c r="I71" t="n">
+        <v>127.4156</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2523,6 +2953,12 @@
           <t>중심 상업/유흥 번화가 및 유동인구 집중</t>
         </is>
       </c>
+      <c r="H72" t="n">
+        <v>35.5698</v>
+      </c>
+      <c r="I72" t="n">
+        <v>129.3328</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2552,6 +2988,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H73" t="n">
+        <v>35.5438</v>
+      </c>
+      <c r="I73" t="n">
+        <v>129.3301</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2581,6 +3023,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H74" t="n">
+        <v>35.5049</v>
+      </c>
+      <c r="I74" t="n">
+        <v>129.4167</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2610,6 +3058,12 @@
           <t>산업단지 및 다문화/공업 밀집</t>
         </is>
       </c>
+      <c r="H75" t="n">
+        <v>35.5828</v>
+      </c>
+      <c r="I75" t="n">
+        <v>129.3615</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2639,6 +3093,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H76" t="n">
+        <v>35.5398</v>
+      </c>
+      <c r="I76" t="n">
+        <v>129.2374</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2668,6 +3128,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H77" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="I77" t="n">
+        <v>127.289</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2697,6 +3163,12 @@
           <t>대도시 중심 도심권 및 복합 상권</t>
         </is>
       </c>
+      <c r="H78" t="n">
+        <v>37.6584</v>
+      </c>
+      <c r="I78" t="n">
+        <v>126.832</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2726,6 +3198,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H79" t="n">
+        <v>37.4292</v>
+      </c>
+      <c r="I79" t="n">
+        <v>126.9877</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2755,6 +3233,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H80" t="n">
+        <v>37.4786</v>
+      </c>
+      <c r="I80" t="n">
+        <v>126.8646</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2784,6 +3268,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H81" t="n">
+        <v>37.4294</v>
+      </c>
+      <c r="I81" t="n">
+        <v>127.2551</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2813,6 +3303,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H82" t="n">
+        <v>37.5943</v>
+      </c>
+      <c r="I82" t="n">
+        <v>127.1296</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2842,6 +3338,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H83" t="n">
+        <v>37.3614</v>
+      </c>
+      <c r="I83" t="n">
+        <v>126.9352</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2871,6 +3373,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H84" t="n">
+        <v>37.6152</v>
+      </c>
+      <c r="I84" t="n">
+        <v>126.7157</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2900,6 +3408,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H85" t="n">
+        <v>37.636</v>
+      </c>
+      <c r="I85" t="n">
+        <v>127.2165</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2929,6 +3443,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H86" t="n">
+        <v>37.9036</v>
+      </c>
+      <c r="I86" t="n">
+        <v>127.0607</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2958,6 +3478,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H87" t="n">
+        <v>37.5034</v>
+      </c>
+      <c r="I87" t="n">
+        <v>126.766</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2987,6 +3513,12 @@
           <t>대도시 중심 도심권 및 복합 상권</t>
         </is>
       </c>
+      <c r="H88" t="n">
+        <v>37.4201</v>
+      </c>
+      <c r="I88" t="n">
+        <v>127.1265</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3016,6 +3548,12 @@
           <t>대도시 중심 도심권 및 복합 상권</t>
         </is>
       </c>
+      <c r="H89" t="n">
+        <v>37.2636</v>
+      </c>
+      <c r="I89" t="n">
+        <v>127.0286</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3045,6 +3583,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H90" t="n">
+        <v>37.3802</v>
+      </c>
+      <c r="I90" t="n">
+        <v>126.8029</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3074,6 +3618,12 @@
           <t>산업단지 및 다문화/공업 밀집</t>
         </is>
       </c>
+      <c r="H91" t="n">
+        <v>37.3219</v>
+      </c>
+      <c r="I91" t="n">
+        <v>126.8309</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3103,6 +3653,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H92" t="n">
+        <v>37.008</v>
+      </c>
+      <c r="I92" t="n">
+        <v>127.2798</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3132,6 +3688,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H93" t="n">
+        <v>37.3943</v>
+      </c>
+      <c r="I93" t="n">
+        <v>126.9568</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3161,6 +3723,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H94" t="n">
+        <v>37.7853</v>
+      </c>
+      <c r="I94" t="n">
+        <v>127.0458</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3190,6 +3758,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H95" t="n">
+        <v>37.2984</v>
+      </c>
+      <c r="I95" t="n">
+        <v>127.6371</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3219,6 +3793,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H96" t="n">
+        <v>37.1498</v>
+      </c>
+      <c r="I96" t="n">
+        <v>127.0772</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3248,6 +3828,12 @@
           <t>대도시 중심 도심권 및 복합 상권</t>
         </is>
       </c>
+      <c r="H97" t="n">
+        <v>37.2411</v>
+      </c>
+      <c r="I97" t="n">
+        <v>127.1776</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3277,6 +3863,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H98" t="n">
+        <v>37.3448</v>
+      </c>
+      <c r="I98" t="n">
+        <v>126.9682</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3306,6 +3898,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H99" t="n">
+        <v>37.7381</v>
+      </c>
+      <c r="I99" t="n">
+        <v>127.0337</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3335,6 +3933,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H100" t="n">
+        <v>37.2723</v>
+      </c>
+      <c r="I100" t="n">
+        <v>127.435</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3364,6 +3968,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H101" t="n">
+        <v>37.76</v>
+      </c>
+      <c r="I101" t="n">
+        <v>126.7799</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3393,6 +4003,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H102" t="n">
+        <v>36.9921</v>
+      </c>
+      <c r="I102" t="n">
+        <v>127.1129</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3422,6 +4038,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H103" t="n">
+        <v>37.8949</v>
+      </c>
+      <c r="I103" t="n">
+        <v>127.2003</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3451,6 +4073,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H104" t="n">
+        <v>37.5393</v>
+      </c>
+      <c r="I104" t="n">
+        <v>127.2148</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3480,6 +4108,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H105" t="n">
+        <v>37.1995</v>
+      </c>
+      <c r="I105" t="n">
+        <v>126.8315</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3509,6 +4143,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H106" t="n">
+        <v>38.0964</v>
+      </c>
+      <c r="I106" t="n">
+        <v>127.0747</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3538,6 +4178,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H107" t="n">
+        <v>37.8315</v>
+      </c>
+      <c r="I107" t="n">
+        <v>127.5097</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3567,6 +4213,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H108" t="n">
+        <v>37.4917</v>
+      </c>
+      <c r="I108" t="n">
+        <v>127.4876</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3596,6 +4248,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H109" t="n">
+        <v>37.7519</v>
+      </c>
+      <c r="I109" t="n">
+        <v>128.8761</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3625,6 +4283,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H110" t="n">
+        <v>37.5247</v>
+      </c>
+      <c r="I110" t="n">
+        <v>129.1143</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3654,6 +4318,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H111" t="n">
+        <v>37.4499</v>
+      </c>
+      <c r="I111" t="n">
+        <v>129.1652</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3683,6 +4353,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H112" t="n">
+        <v>38.207</v>
+      </c>
+      <c r="I112" t="n">
+        <v>128.5918</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3712,6 +4388,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H113" t="n">
+        <v>37.3422</v>
+      </c>
+      <c r="I113" t="n">
+        <v>127.9202</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3741,6 +4423,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H114" t="n">
+        <v>37.8813</v>
+      </c>
+      <c r="I114" t="n">
+        <v>127.7298</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3770,6 +4458,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H115" t="n">
+        <v>37.1641</v>
+      </c>
+      <c r="I115" t="n">
+        <v>128.9856</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3799,6 +4493,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H116" t="n">
+        <v>37.6972</v>
+      </c>
+      <c r="I116" t="n">
+        <v>127.8887</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3828,6 +4528,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H117" t="n">
+        <v>37.4918</v>
+      </c>
+      <c r="I117" t="n">
+        <v>127.985</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3857,6 +4563,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H118" t="n">
+        <v>37.1838</v>
+      </c>
+      <c r="I118" t="n">
+        <v>128.4619</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3886,6 +4598,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H119" t="n">
+        <v>37.3705</v>
+      </c>
+      <c r="I119" t="n">
+        <v>128.3902</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3915,6 +4633,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H120" t="n">
+        <v>37.3806</v>
+      </c>
+      <c r="I120" t="n">
+        <v>128.6608</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3944,6 +4668,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H121" t="n">
+        <v>38.1468</v>
+      </c>
+      <c r="I121" t="n">
+        <v>127.3134</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3973,6 +4703,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H122" t="n">
+        <v>38.1062</v>
+      </c>
+      <c r="I122" t="n">
+        <v>127.7082</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4002,6 +4738,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H123" t="n">
+        <v>38.1079</v>
+      </c>
+      <c r="I123" t="n">
+        <v>127.9897</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4031,6 +4773,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H124" t="n">
+        <v>38.0697</v>
+      </c>
+      <c r="I124" t="n">
+        <v>128.1704</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4060,6 +4808,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H125" t="n">
+        <v>38.3806</v>
+      </c>
+      <c r="I125" t="n">
+        <v>128.4678</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4089,6 +4843,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H126" t="n">
+        <v>38.0754</v>
+      </c>
+      <c r="I126" t="n">
+        <v>128.6189</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4118,6 +4878,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H127" t="n">
+        <v>36.7407</v>
+      </c>
+      <c r="I127" t="n">
+        <v>127.7162</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4147,6 +4913,12 @@
           <t>대도시 중심 도심권 및 복합 상권</t>
         </is>
       </c>
+      <c r="H128" t="n">
+        <v>36.6007</v>
+      </c>
+      <c r="I128" t="n">
+        <v>127.5812</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4176,6 +4948,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H129" t="n">
+        <v>36.2507</v>
+      </c>
+      <c r="I129" t="n">
+        <v>127.1312</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4205,6 +4983,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H130" t="n">
+        <v>36.4607</v>
+      </c>
+      <c r="I130" t="n">
+        <v>126.8162</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4234,6 +5018,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H131" t="n">
+        <v>36.7407</v>
+      </c>
+      <c r="I131" t="n">
+        <v>127.3562</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4263,6 +5053,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H132" t="n">
+        <v>36.2857</v>
+      </c>
+      <c r="I132" t="n">
+        <v>126.8612</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4292,6 +5088,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H133" t="n">
+        <v>36.9507</v>
+      </c>
+      <c r="I133" t="n">
+        <v>127.7612</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4321,6 +5123,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H134" t="n">
+        <v>36.7757</v>
+      </c>
+      <c r="I134" t="n">
+        <v>127.3562</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4350,6 +5158,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H135" t="n">
+        <v>37.1257</v>
+      </c>
+      <c r="I135" t="n">
+        <v>127.7162</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4379,6 +5193,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H136" t="n">
+        <v>36.4257</v>
+      </c>
+      <c r="I136" t="n">
+        <v>128.0312</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4408,6 +5228,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H137" t="n">
+        <v>36.9857</v>
+      </c>
+      <c r="I137" t="n">
+        <v>127.2212</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4437,6 +5263,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H138" t="n">
+        <v>36.7634</v>
+      </c>
+      <c r="I138" t="n">
+        <v>126.305</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4466,6 +5298,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H139" t="n">
+        <v>36.6584</v>
+      </c>
+      <c r="I139" t="n">
+        <v>127.07</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4495,6 +5333,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H140" t="n">
+        <v>36.1684</v>
+      </c>
+      <c r="I140" t="n">
+        <v>126.53</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4524,6 +5368,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H141" t="n">
+        <v>37.0084</v>
+      </c>
+      <c r="I141" t="n">
+        <v>126.35</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4553,6 +5403,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H142" t="n">
+        <v>36.4834</v>
+      </c>
+      <c r="I142" t="n">
+        <v>126.935</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4582,6 +5438,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H143" t="n">
+        <v>36.2734</v>
+      </c>
+      <c r="I143" t="n">
+        <v>126.44</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4611,6 +5473,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H144" t="n">
+        <v>36.7284</v>
+      </c>
+      <c r="I144" t="n">
+        <v>126.89</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4640,6 +5508,12 @@
           <t>대도시 중심 도심권 및 복합 상권</t>
         </is>
       </c>
+      <c r="H145" t="n">
+        <v>36.2384</v>
+      </c>
+      <c r="I145" t="n">
+        <v>126.845</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4669,6 +5543,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H146" t="n">
+        <v>35.9934</v>
+      </c>
+      <c r="I146" t="n">
+        <v>126.98</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4698,6 +5578,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H147" t="n">
+        <v>36.6584</v>
+      </c>
+      <c r="I147" t="n">
+        <v>126.62</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4727,6 +5613,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H148" t="n">
+        <v>36.3784</v>
+      </c>
+      <c r="I148" t="n">
+        <v>126.53</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4756,6 +5648,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H149" t="n">
+        <v>36.1334</v>
+      </c>
+      <c r="I149" t="n">
+        <v>126.935</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4785,6 +5683,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H150" t="n">
+        <v>36.6584</v>
+      </c>
+      <c r="I150" t="n">
+        <v>126.17</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4814,6 +5718,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H151" t="n">
+        <v>36.3084</v>
+      </c>
+      <c r="I151" t="n">
+        <v>126.125</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4843,6 +5753,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H152" t="n">
+        <v>36.0984</v>
+      </c>
+      <c r="I152" t="n">
+        <v>126.125</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4872,6 +5788,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H153" t="n">
+        <v>35.9975</v>
+      </c>
+      <c r="I153" t="n">
+        <v>127.423</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4901,6 +5823,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H154" t="n">
+        <v>35.6125</v>
+      </c>
+      <c r="I154" t="n">
+        <v>127.243</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4930,6 +5858,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H155" t="n">
+        <v>35.6825</v>
+      </c>
+      <c r="I155" t="n">
+        <v>126.478</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4959,6 +5893,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H156" t="n">
+        <v>35.7525</v>
+      </c>
+      <c r="I156" t="n">
+        <v>127.333</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4988,6 +5928,12 @@
           <t>대도시 중심 도심권 및 복합 상권</t>
         </is>
       </c>
+      <c r="H157" t="n">
+        <v>35.4375</v>
+      </c>
+      <c r="I157" t="n">
+        <v>127.738</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5017,6 +5963,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H158" t="n">
+        <v>36.1025</v>
+      </c>
+      <c r="I158" t="n">
+        <v>127.018</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5046,6 +5998,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H159" t="n">
+        <v>35.4375</v>
+      </c>
+      <c r="I159" t="n">
+        <v>126.523</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5075,6 +6033,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H160" t="n">
+        <v>35.9275</v>
+      </c>
+      <c r="I160" t="n">
+        <v>127.738</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5104,6 +6068,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H161" t="n">
+        <v>35.9625</v>
+      </c>
+      <c r="I161" t="n">
+        <v>127.693</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5133,6 +6103,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H162" t="n">
+        <v>35.3675</v>
+      </c>
+      <c r="I162" t="n">
+        <v>127.648</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5162,6 +6138,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H163" t="n">
+        <v>36.1375</v>
+      </c>
+      <c r="I163" t="n">
+        <v>127.423</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5191,6 +6173,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H164" t="n">
+        <v>35.6475</v>
+      </c>
+      <c r="I164" t="n">
+        <v>127.828</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5220,6 +6208,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H165" t="n">
+        <v>35.3675</v>
+      </c>
+      <c r="I165" t="n">
+        <v>127.063</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5249,6 +6243,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H166" t="n">
+        <v>35.2275</v>
+      </c>
+      <c r="I166" t="n">
+        <v>127.513</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5278,6 +6278,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H167" t="n">
+        <v>34.5879</v>
+      </c>
+      <c r="I167" t="n">
+        <v>127.081</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5307,6 +6313,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H168" t="n">
+        <v>34.8679</v>
+      </c>
+      <c r="I168" t="n">
+        <v>126.406</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5336,6 +6348,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H169" t="n">
+        <v>35.2179</v>
+      </c>
+      <c r="I169" t="n">
+        <v>127.531</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5365,6 +6383,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H170" t="n">
+        <v>35.2879</v>
+      </c>
+      <c r="I170" t="n">
+        <v>127.666</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5394,6 +6418,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H171" t="n">
+        <v>35.3579</v>
+      </c>
+      <c r="I171" t="n">
+        <v>126.316</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5423,6 +6453,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H172" t="n">
+        <v>34.5879</v>
+      </c>
+      <c r="I172" t="n">
+        <v>127.531</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5452,6 +6488,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H173" t="n">
+        <v>35.1129</v>
+      </c>
+      <c r="I173" t="n">
+        <v>127.171</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5481,6 +6523,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H174" t="n">
+        <v>34.5179</v>
+      </c>
+      <c r="I174" t="n">
+        <v>127.261</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5510,6 +6558,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H175" t="n">
+        <v>35.0079</v>
+      </c>
+      <c r="I175" t="n">
+        <v>127.216</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5539,6 +6593,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H176" t="n">
+        <v>35.3929</v>
+      </c>
+      <c r="I176" t="n">
+        <v>127.531</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5568,6 +6628,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H177" t="n">
+        <v>35.3229</v>
+      </c>
+      <c r="I177" t="n">
+        <v>127.216</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5597,6 +6663,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H178" t="n">
+        <v>34.7629</v>
+      </c>
+      <c r="I178" t="n">
+        <v>126.946</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5626,6 +6698,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H179" t="n">
+        <v>35.0429</v>
+      </c>
+      <c r="I179" t="n">
+        <v>126.856</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5655,6 +6733,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H180" t="n">
+        <v>35.1479</v>
+      </c>
+      <c r="I180" t="n">
+        <v>127.486</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5684,6 +6768,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H181" t="n">
+        <v>34.8329</v>
+      </c>
+      <c r="I181" t="n">
+        <v>126.901</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5713,6 +6803,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H182" t="n">
+        <v>34.4129</v>
+      </c>
+      <c r="I182" t="n">
+        <v>127.666</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5742,6 +6838,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H183" t="n">
+        <v>34.5529</v>
+      </c>
+      <c r="I183" t="n">
+        <v>126.631</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5771,6 +6873,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H184" t="n">
+        <v>35.0079</v>
+      </c>
+      <c r="I184" t="n">
+        <v>126.856</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5800,6 +6908,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H185" t="n">
+        <v>34.3429</v>
+      </c>
+      <c r="I185" t="n">
+        <v>127.216</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5829,6 +6943,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H186" t="n">
+        <v>35.2529</v>
+      </c>
+      <c r="I186" t="n">
+        <v>127.126</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5858,6 +6978,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H187" t="n">
+        <v>34.7279</v>
+      </c>
+      <c r="I187" t="n">
+        <v>127.396</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5887,6 +7013,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H188" t="n">
+        <v>35.2179</v>
+      </c>
+      <c r="I188" t="n">
+        <v>126.586</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5916,6 +7048,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H189" t="n">
+        <v>36.191</v>
+      </c>
+      <c r="I189" t="n">
+        <v>129.1806</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5945,6 +7083,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H190" t="n">
+        <v>36.156</v>
+      </c>
+      <c r="I190" t="n">
+        <v>128.2806</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5974,6 +7118,12 @@
           <t>산업단지 및 다문화/공업 밀집</t>
         </is>
       </c>
+      <c r="H191" t="n">
+        <v>36.366</v>
+      </c>
+      <c r="I191" t="n">
+        <v>128.4606</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6003,6 +7153,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H192" t="n">
+        <v>36.401</v>
+      </c>
+      <c r="I192" t="n">
+        <v>128.2356</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6032,6 +7188,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H193" t="n">
+        <v>36.261</v>
+      </c>
+      <c r="I193" t="n">
+        <v>128.9106</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6061,6 +7223,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H194" t="n">
+        <v>36.401</v>
+      </c>
+      <c r="I194" t="n">
+        <v>129.1806</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6090,6 +7258,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H195" t="n">
+        <v>36.051</v>
+      </c>
+      <c r="I195" t="n">
+        <v>128.2806</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6119,6 +7293,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H196" t="n">
+        <v>36.156</v>
+      </c>
+      <c r="I196" t="n">
+        <v>128.0106</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6148,6 +7328,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H197" t="n">
+        <v>36.156</v>
+      </c>
+      <c r="I197" t="n">
+        <v>128.0556</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6177,6 +7363,12 @@
           <t>산업단지 및 다문화/공업 밀집</t>
         </is>
       </c>
+      <c r="H198" t="n">
+        <v>37.031</v>
+      </c>
+      <c r="I198" t="n">
+        <v>128.3706</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6206,6 +7398,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H199" t="n">
+        <v>36.611</v>
+      </c>
+      <c r="I199" t="n">
+        <v>128.5506</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6235,6 +7433,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H200" t="n">
+        <v>36.471</v>
+      </c>
+      <c r="I200" t="n">
+        <v>127.8756</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6264,6 +7468,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H201" t="n">
+        <v>37.066</v>
+      </c>
+      <c r="I201" t="n">
+        <v>128.9106</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6293,6 +7503,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H202" t="n">
+        <v>36.051</v>
+      </c>
+      <c r="I202" t="n">
+        <v>128.0556</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6322,6 +7538,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H203" t="n">
+        <v>37.066</v>
+      </c>
+      <c r="I203" t="n">
+        <v>128.4606</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6351,6 +7573,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H204" t="n">
+        <v>36.436</v>
+      </c>
+      <c r="I204" t="n">
+        <v>128.9106</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6380,6 +7608,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H205" t="n">
+        <v>36.541</v>
+      </c>
+      <c r="I205" t="n">
+        <v>128.2356</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6409,6 +7643,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H206" t="n">
+        <v>36.191</v>
+      </c>
+      <c r="I206" t="n">
+        <v>128.8206</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6438,6 +7678,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H207" t="n">
+        <v>36.541</v>
+      </c>
+      <c r="I207" t="n">
+        <v>128.0556</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6467,6 +7713,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H208" t="n">
+        <v>37.031</v>
+      </c>
+      <c r="I208" t="n">
+        <v>128.5506</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6496,6 +7748,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H209" t="n">
+        <v>36.891</v>
+      </c>
+      <c r="I209" t="n">
+        <v>128.0106</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6525,6 +7783,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H210" t="n">
+        <v>36.891</v>
+      </c>
+      <c r="I210" t="n">
+        <v>128.2356</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6554,6 +7818,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H211" t="n">
+        <v>34.9356</v>
+      </c>
+      <c r="I211" t="n">
+        <v>127.5832</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6583,6 +7853,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H212" t="n">
+        <v>35.4606</v>
+      </c>
+      <c r="I212" t="n">
+        <v>128.5282</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6612,6 +7888,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H213" t="n">
+        <v>35.6006</v>
+      </c>
+      <c r="I213" t="n">
+        <v>127.7632</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6641,6 +7923,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H214" t="n">
+        <v>35.3906</v>
+      </c>
+      <c r="I214" t="n">
+        <v>128.0332</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6670,6 +7958,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H215" t="n">
+        <v>35.3906</v>
+      </c>
+      <c r="I215" t="n">
+        <v>127.6282</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6699,6 +7993,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H216" t="n">
+        <v>35.3206</v>
+      </c>
+      <c r="I216" t="n">
+        <v>127.9432</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6728,6 +8028,12 @@
           <t>대도시 중심 도심권 및 복합 상권</t>
         </is>
       </c>
+      <c r="H217" t="n">
+        <v>35.5656</v>
+      </c>
+      <c r="I217" t="n">
+        <v>127.9882</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6757,6 +8063,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H218" t="n">
+        <v>35.7056</v>
+      </c>
+      <c r="I218" t="n">
+        <v>128.3032</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6786,6 +8098,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H219" t="n">
+        <v>35.1106</v>
+      </c>
+      <c r="I219" t="n">
+        <v>128.1682</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6815,6 +8133,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H220" t="n">
+        <v>35.8106</v>
+      </c>
+      <c r="I220" t="n">
+        <v>128.8432</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6844,6 +8168,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H221" t="n">
+        <v>35.6006</v>
+      </c>
+      <c r="I221" t="n">
+        <v>127.5832</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6873,6 +8203,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H222" t="n">
+        <v>35.0056</v>
+      </c>
+      <c r="I222" t="n">
+        <v>127.5382</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6902,6 +8238,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H223" t="n">
+        <v>34.9706</v>
+      </c>
+      <c r="I223" t="n">
+        <v>127.5382</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6931,6 +8273,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H224" t="n">
+        <v>35.1806</v>
+      </c>
+      <c r="I224" t="n">
+        <v>127.8982</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6960,6 +8308,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H225" t="n">
+        <v>35.5656</v>
+      </c>
+      <c r="I225" t="n">
+        <v>128.7982</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6989,6 +8343,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H226" t="n">
+        <v>35.7056</v>
+      </c>
+      <c r="I226" t="n">
+        <v>127.9432</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7018,6 +8378,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H227" t="n">
+        <v>35.0056</v>
+      </c>
+      <c r="I227" t="n">
+        <v>127.5832</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7047,6 +8413,12 @@
           <t>전원형 농어촌 및 고령 주거지</t>
         </is>
       </c>
+      <c r="H228" t="n">
+        <v>35.7056</v>
+      </c>
+      <c r="I228" t="n">
+        <v>128.3032</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7076,6 +8448,12 @@
           <t>주거 밀집 베드타운</t>
         </is>
       </c>
+      <c r="H229" t="n">
+        <v>33.2541</v>
+      </c>
+      <c r="I229" t="n">
+        <v>126.5601</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7104,6 +8482,12 @@
         <is>
           <t>주거 밀집 베드타운</t>
         </is>
+      </c>
+      <c r="H230" t="n">
+        <v>33.4996</v>
+      </c>
+      <c r="I230" t="n">
+        <v>126.5312</v>
       </c>
     </row>
   </sheetData>
